--- a/docs/jbss/jbss.xlsx
+++ b/docs/jbss/jbss.xlsx
@@ -1773,22 +1773,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PV of free cash flow, years 1 to 6</t>
+          <t>PV of free cash flow, years 1 to 5</t>
         </is>
       </c>
       <c r="B3" s="7">
-        <f>SUM(Model!B21:Model!G21)</f>
+        <f>SUM(Model!B21:Model!F21)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Terminal value at the end of year 6</t>
+          <t>Terminal value at the end of year 5</t>
         </is>
       </c>
       <c r="B4" s="7">
-        <f>Model!H19/(Inputs!$B$24-Inputs!$G$6)</f>
+        <f>Model!G19/(Inputs!$B$24-Inputs!$G$6)</f>
         <v/>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>B4/(1+Inputs!$B$24)^6</f>
+        <f>B4/(1+Inputs!$B$24)^5</f>
         <v/>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="B26">
-        <f>IF(ABS(Bridge!B4-(1872544.2947459894))&gt;1e-06,"FAIL","ok")</f>
+        <f>IF(ABS(Bridge!B4-(1809221.5408173827))&gt;1e-06,"FAIL","ok")</f>
         <v/>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="B27">
-        <f>IF(ABS(Bridge!B5-(1180020.5395421663))&gt;1e-06,"FAIL","ok")</f>
+        <f>IF(ABS(Bridge!B5-(1231325.7803918268))&gt;1e-06,"FAIL","ok")</f>
         <v/>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="B28">
-        <f>IF(ABS(Bridge!B3-(337802.0659080064))&gt;1e-06,"FAIL","ok")</f>
+        <f>IF(ABS(Bridge!B3-(286496.8250583469))&gt;1e-06,"FAIL","ok")</f>
         <v/>
       </c>
     </row>

--- a/docs/jbss/jbss.xlsx
+++ b/docs/jbss/jbss.xlsx
@@ -1773,22 +1773,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PV of free cash flow, years 1 to 5</t>
+          <t>PV of free cash flow, years 1 to 6</t>
         </is>
       </c>
       <c r="B3" s="7">
-        <f>SUM(Model!B21:Model!F21)</f>
+        <f>SUM(Model!B21:Model!G21)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Terminal value at the end of year 5</t>
+          <t>Terminal value at the end of year 6</t>
         </is>
       </c>
       <c r="B4" s="7">
-        <f>Model!G19/(Inputs!$B$24-Inputs!$G$6)</f>
+        <f>Model!H19/(Inputs!$B$24-Inputs!$G$6)</f>
         <v/>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>B4/(1+Inputs!$B$24)^5</f>
+        <f>B4/(1+Inputs!$B$24)^6</f>
         <v/>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="B26">
-        <f>IF(ABS(Bridge!B4-(1809221.5408173827))&gt;1e-06,"FAIL","ok")</f>
+        <f>IF(ABS(Bridge!B4-(1872544.2947459894))&gt;1e-06,"FAIL","ok")</f>
         <v/>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="B27">
-        <f>IF(ABS(Bridge!B5-(1231325.7803918268))&gt;1e-06,"FAIL","ok")</f>
+        <f>IF(ABS(Bridge!B5-(1180020.5395421663))&gt;1e-06,"FAIL","ok")</f>
         <v/>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="B28">
-        <f>IF(ABS(Bridge!B3-(286496.8250583469))&gt;1e-06,"FAIL","ok")</f>
+        <f>IF(ABS(Bridge!B3-(337802.0659080064))&gt;1e-06,"FAIL","ok")</f>
         <v/>
       </c>
     </row>
